--- a/cookbook/spreadsheet-recalc/examples/good/dcf_model.xlsx
+++ b/cookbook/spreadsheet-recalc/examples/good/dcf_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -467,31 +467,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Year 1 Cash Flow</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Year 2 Cash Flow</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Year 3 Cash Flow</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5100</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -505,13 +485,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,50 +507,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cash Flow</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <f>Assumptions!B2</f>
-        <v/>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <f>B2*C2</f>
-        <v/>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PV of FCF</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3">
-        <f>Assumptions!B4</f>
-        <v/>
-      </c>
-      <c r="C3">
+      <c r="B3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D3">
+        <f>B3-C3</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>D3*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>D3-E3</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>F3</f>
+        <v/>
+      </c>
+      <c r="H3">
         <f>1/(1+Assumptions!$B$3)^A3</f>
         <v/>
       </c>
-      <c r="D3">
-        <f>B3*C3</f>
+      <c r="I3">
+        <f>G3*H3</f>
         <v/>
       </c>
     </row>
@@ -573,16 +585,34 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4">
-        <f>Assumptions!B5</f>
-        <v/>
-      </c>
-      <c r="C4">
+      <c r="B4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="D4">
+        <f>B4-C4</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>D4*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>D4-E4</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>F4</f>
+        <v/>
+      </c>
+      <c r="H4">
         <f>1/(1+Assumptions!$B$3)^A4</f>
         <v/>
       </c>
-      <c r="D4">
-        <f>B4*C4</f>
+      <c r="I4">
+        <f>G4*H4</f>
         <v/>
       </c>
     </row>
@@ -590,16 +620,34 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5">
-        <f>Assumptions!B6</f>
-        <v/>
-      </c>
-      <c r="C5">
+      <c r="B5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D5">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>D5*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>D5-E5</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="H5">
         <f>1/(1+Assumptions!$B$3)^A5</f>
         <v/>
       </c>
-      <c r="D5">
-        <f>B5*C5</f>
+      <c r="I5">
+        <f>G5*H5</f>
         <v/>
       </c>
     </row>
@@ -614,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -640,18 +688,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>SUM(Projections!D2:D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IRR (approx)</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>Assumptions!B3</f>
+        <f>Assumptions!B2+SUM(Projections!I3:I5)</f>
         <v/>
       </c>
     </row>
